--- a/data/trans_orig/Q61A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q61A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de meses que lleva en paro</t>
+          <t>Número medio de meses que lleva en paro (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,34</t>
+          <t>3,01; 5,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 11,37</t>
+          <t>8,57; 11,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 11,88</t>
+          <t>6,8; 12,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 16,0</t>
+          <t>4,81; 17,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,38</t>
+          <t>4,12; 7,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 14,91</t>
+          <t>9,62; 14,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 14,41</t>
+          <t>8,69; 14,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 12,34</t>
+          <t>4,64; 10,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,92</t>
+          <t>3,82; 5,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 12,1</t>
+          <t>9,33; 11,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,33; 12,08</t>
+          <t>8,28; 12,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 12,95</t>
+          <t>5,55; 12,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,2</t>
+          <t>3,4; 5,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 15,4</t>
+          <t>10,6; 15,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,77; 17,94</t>
+          <t>11,81; 17,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 18,55</t>
+          <t>6,64; 18,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 7,29</t>
+          <t>4,41; 7,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,11; 17,61</t>
+          <t>12,94; 17,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,62; 21,82</t>
+          <t>15,73; 21,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 14,31</t>
+          <t>8,38; 13,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,62</t>
+          <t>4,04; 5,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,11; 15,78</t>
+          <t>12,14; 15,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,3; 18,58</t>
+          <t>14,45; 18,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 13,91</t>
+          <t>8,41; 13,9</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,6</t>
+          <t>3,55; 8,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,59; 14,84</t>
+          <t>11,63; 14,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 22,79</t>
+          <t>16,48; 22,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 16,58</t>
+          <t>9,43; 16,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 15,15</t>
+          <t>6,46; 15,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,65; 23,56</t>
+          <t>16,47; 23,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,88; 29,18</t>
+          <t>19,55; 28,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,0; 18,34</t>
+          <t>12,77; 18,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 10,91</t>
+          <t>5,79; 11,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,47; 18,2</t>
+          <t>14,42; 18,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18,86; 24,33</t>
+          <t>19,24; 24,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,13; 16,75</t>
+          <t>12,24; 16,51</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 14,25</t>
+          <t>6,31; 14,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,09; 18,44</t>
+          <t>13,9; 18,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 26,19</t>
+          <t>20,21; 26,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,43; 40,29</t>
+          <t>19,38; 39,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 38,93</t>
+          <t>7,01; 40,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 26,17</t>
+          <t>15,63; 25,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,48; 32,44</t>
+          <t>20,88; 32,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,16; 40,46</t>
+          <t>24,89; 40,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 25,46</t>
+          <t>8,1; 25,79</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,29; 20,1</t>
+          <t>15,39; 20,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,67; 27,77</t>
+          <t>21,8; 28,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,29; 36,0</t>
+          <t>24,17; 36,47</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 45,13</t>
+          <t>8,93; 38,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,69; 39,15</t>
+          <t>23,42; 39,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,21; 35,36</t>
+          <t>24,65; 35,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,56; 40,93</t>
+          <t>24,6; 41,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 14,95</t>
+          <t>5,27; 14,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,48; 67,28</t>
+          <t>21,36; 61,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,74; 41,55</t>
+          <t>25,99; 41,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,76; 51,46</t>
+          <t>30,82; 50,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 29,75</t>
+          <t>8,98; 29,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,28; 40,15</t>
+          <t>23,86; 39,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,0; 36,43</t>
+          <t>27,34; 36,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>29,76; 42,06</t>
+          <t>28,85; 41,62</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,27; 55,69</t>
+          <t>10,96; 60,0</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,89</t>
+          <t>5,08; 8,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,74; 16,59</t>
+          <t>13,74; 16,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,12; 21,33</t>
+          <t>18,23; 21,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,54; 25,22</t>
+          <t>17,51; 25,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,57</t>
+          <t>6,21; 10,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,38; 20,92</t>
+          <t>16,35; 21,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,54; 25,21</t>
+          <t>20,8; 25,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,5; 27,04</t>
+          <t>20,39; 26,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,68</t>
+          <t>5,93; 8,74</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,28; 17,63</t>
+          <t>15,25; 17,63</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,59</t>
+          <t>19,8; 22,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,92; 24,68</t>
+          <t>19,81; 24,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q61A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q61A-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,6</t>
+          <t>10,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>6,53</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,65</t>
+          <t>9,05</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,33</t>
+          <t>2,94; 5,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 11,39</t>
+          <t>8,29; 11,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,8; 12,18</t>
+          <t>6,69; 11,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 17,04</t>
+          <t>5,84; 16,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,66</t>
+          <t>4,0; 7,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 14,88</t>
+          <t>9,61; 14,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,69; 14,33</t>
+          <t>8,59; 14,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 10,81</t>
+          <t>4,38; 11,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,94</t>
+          <t>3,76; 5,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,33; 11,85</t>
+          <t>9,34; 12,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,13</t>
+          <t>8,29; 12,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,55; 12,75</t>
+          <t>5,8; 12,74</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,82</t>
+          <t>9,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,61</t>
+          <t>11,06</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,68</t>
+          <t>10,66</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,24</t>
+          <t>3,37; 5,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,85</t>
+          <t>10,63; 15,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,81; 17,63</t>
+          <t>11,84; 17,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 18,26</t>
+          <t>6,51; 16,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,41; 7,54</t>
+          <t>4,36; 7,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,94; 17,47</t>
+          <t>12,96; 17,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 21,79</t>
+          <t>15,76; 21,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,38; 13,96</t>
+          <t>8,44; 16,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,69</t>
+          <t>4,06; 5,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,14; 15,62</t>
+          <t>12,11; 15,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14,45; 18,62</t>
+          <t>14,28; 18,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,9</t>
+          <t>8,49; 14,24</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,53</t>
+          <t>11,69</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,31</t>
+          <t>15,21</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,34</t>
+          <t>13,97</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 8,42</t>
+          <t>3,59; 8,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,63; 14,95</t>
+          <t>11,63; 14,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,48; 22,93</t>
+          <t>16,56; 22,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 16,64</t>
+          <t>8,8; 15,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 15,18</t>
+          <t>6,34; 15,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,47; 23,61</t>
+          <t>16,41; 23,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,55; 28,17</t>
+          <t>20,11; 28,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 18,07</t>
+          <t>12,89; 17,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 11,0</t>
+          <t>5,82; 10,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,42; 18,33</t>
+          <t>14,44; 18,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19,24; 24,57</t>
+          <t>18,83; 24,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,24; 16,51</t>
+          <t>12,17; 16,17</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26,14</t>
+          <t>24,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>31,29</t>
+          <t>31,81</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,1</t>
+          <t>28,77</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 14,69</t>
+          <t>6,09; 14,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,9; 18,54</t>
+          <t>14,02; 18,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,21; 26,54</t>
+          <t>20,3; 26,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,38; 39,11</t>
+          <t>18,53; 37,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,01; 40,76</t>
+          <t>6,78; 39,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,63; 25,79</t>
+          <t>15,38; 25,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,88; 32,86</t>
+          <t>21,81; 33,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,89; 40,84</t>
+          <t>25,68; 41,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 25,79</t>
+          <t>7,66; 23,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,39; 20,32</t>
+          <t>15,36; 20,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,8; 28,0</t>
+          <t>21,74; 27,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,17; 36,47</t>
+          <t>23,49; 35,57</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31,51</t>
+          <t>31,54</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>38,79</t>
+          <t>39,1</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35,03</t>
+          <t>35,21</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,93; 38,69</t>
+          <t>9,03; 35,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>23,42; 39,87</t>
+          <t>22,91; 39,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24,65; 35,72</t>
+          <t>24,65; 36,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24,6; 41,25</t>
+          <t>24,57; 40,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 14,62</t>
+          <t>5,44; 14,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,36; 61,15</t>
+          <t>21,96; 66,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,99; 41,85</t>
+          <t>26,72; 41,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>30,82; 50,64</t>
+          <t>31,15; 50,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,98; 29,91</t>
+          <t>9,05; 28,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23,86; 39,98</t>
+          <t>24,14; 39,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,34; 36,31</t>
+          <t>26,74; 36,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,85; 41,62</t>
+          <t>29,6; 43,05</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,23</t>
+          <t>8,1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>40,45</t>
+          <t>41,1</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,73</t>
+          <t>26,27</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,15; 72,98</t>
+          <t>12,15; 72,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,38; 58,31</t>
+          <t>3,4; 58,81</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,96; 60,0</t>
+          <t>9,71; 55,36</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20,87</t>
+          <t>20,29</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23,15</t>
+          <t>23,36</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,15</t>
+          <t>22,02</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,78</t>
+          <t>5,02; 8,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,74; 16,52</t>
+          <t>13,76; 16,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,23; 21,43</t>
+          <t>18,09; 21,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,51; 25,29</t>
+          <t>17,37; 24,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,69</t>
+          <t>6,23; 11,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,01</t>
+          <t>16,42; 20,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,8; 25,22</t>
+          <t>20,77; 25,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,39; 26,96</t>
+          <t>20,59; 26,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,74</t>
+          <t>5,91; 8,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15,25; 17,63</t>
+          <t>15,23; 17,64</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,52</t>
+          <t>19,72; 22,55</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,81; 24,9</t>
+          <t>19,66; 24,45</t>
         </is>
       </c>
     </row>
